--- a/artfynd/A 42105-2024 artfynd.xlsx
+++ b/artfynd/A 42105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120553330</v>
+        <v>120553327</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520220</v>
+        <v>520181</v>
       </c>
       <c r="R2" t="n">
-        <v>6952779</v>
+        <v>6952785</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,12 +762,9 @@
           <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
         </is>
       </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga med mossa på</t>
+          <t>senvuxna granar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120553328</v>
+        <v>120553344</v>
       </c>
       <c r="B3" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520186</v>
+        <v>520132</v>
       </c>
       <c r="R3" t="n">
-        <v>6952793</v>
+        <v>6952746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +870,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+          <t>170-årig hänglavsdraperad barrnaturskog</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov brandhögstubbe</t>
+          <t>senvuxna granar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,12 +900,7 @@
         <v>120553329</v>
       </c>
       <c r="B4" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,37 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120553344</v>
+        <v>120553330</v>
       </c>
       <c r="B5" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520132</v>
+        <v>520220</v>
       </c>
       <c r="R5" t="n">
-        <v>6952746</v>
+        <v>6952779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,12 +1095,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>170-årig hänglavsdraperad barrnaturskog</t>
-        </is>
+          <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>senvuxna granar</t>
+          <t>1 substratenheter # gammal tallåga med mossa på</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,15 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120553327</v>
+        <v>120553328</v>
       </c>
       <c r="B6" t="n">
-        <v>78628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520181</v>
+        <v>520186</v>
       </c>
       <c r="R6" t="n">
-        <v>6952785</v>
+        <v>6952793</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,9 +1212,12 @@
           <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
         </is>
       </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>senvuxna granar</t>
+          <t>1 substratenheter # grov brandhögstubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1257,6 +1232,120 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120553343</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodbergsplatåns sydöstra del, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>520056</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6952817</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>130-årig hällmarkstallskog med inslag av gammal tall och gott om torrakor</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 42105-2024 artfynd.xlsx
+++ b/artfynd/A 42105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553327</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553344</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553329</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,8 +1380,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>